--- a/files/九龙-启德-Double Coast I.xlsx
+++ b/files/九龙-启德-Double Coast I.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -959,7 +959,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18935,7 +18935,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23420,7 +23420,7 @@
           <t>A | 1276呎 (4+房)
 $3152万
 $24,700/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -23429,7 +23429,7 @@
           <t>C | 419呎 (2房)
 $849万
 $20,255/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -23445,7 +23445,7 @@
           <t>E | 455呎 (2房)
 $977万
 $21,473/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -23453,7 +23453,7 @@
           <t>F | 1260呎 (4+房)
 $2900万
 $23,016/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -23473,7 +23473,7 @@
           <t>A | 439呎 (2房)
 $958万
 $21,825/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -23481,7 +23481,7 @@
           <t>B | 627呎 (3房)
 $1362万
 $21,730/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -23489,7 +23489,7 @@
           <t>C | 420呎 (2房)
 $832万
 $19,810/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -23497,7 +23497,7 @@
           <t>D | 477呎 (2房)
 $996万
 $20,887/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -23505,7 +23505,7 @@
           <t>E | 463呎 (2房)
 $916万
 $19,784/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -23513,7 +23513,7 @@
           <t>F | 325呎 (1房)
 $603万
 $18,545/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -23521,7 +23521,7 @@
           <t>G | 265呎 (开放式)
 $495万
 $18,683/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -23529,7 +23529,7 @@
           <t>H | 324呎 (1房)
 $599万
 $18,497/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -23537,7 +23537,7 @@
           <t>J | 437呎 (2房)
 $823万
 $18,833/呎
-(25年-05月-04日)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -23545,7 +23545,7 @@
           <t>K | 435呎 (2房)
 $815万
 $18,736/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -23553,7 +23553,7 @@
           <t>L | 320呎 (1房)
 $590万
 $18,422/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -23568,7 +23568,7 @@
           <t>A | 439呎 (2房)
 $1008万
 $22,966/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -23576,7 +23576,7 @@
           <t>B | 628呎 (3房)
 $1394万
 $22,201/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -23584,7 +23584,7 @@
           <t>C | 420呎 (2房)
 $826万
 $19,667/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -23600,7 +23600,7 @@
           <t>E | 462呎 (2房)
 $915万
 $19,805/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -23608,7 +23608,7 @@
           <t>F | 325呎 (1房)
 $598万
 $18,394/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -23616,7 +23616,7 @@
           <t>G | 265呎 (开放式)
 $486万
 $18,332/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -23624,7 +23624,7 @@
           <t>H | 324呎 (1房)
 $608万
 $18,769/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -23632,7 +23632,7 @@
           <t>J | 440呎 (2房)
 $814万
 $18,500/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -23640,7 +23640,7 @@
           <t>K | 437呎 (2房)
 $810万
 $18,535/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -23648,7 +23648,7 @@
           <t>L | 320呎 (1房)
 $580万
 $18,125/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -23671,7 +23671,7 @@
           <t>B | 628呎 (3房)
 $1404万
 $22,363/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -23679,7 +23679,7 @@
           <t>C | 420呎 (2房)
 $843万
 $20,071/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -23695,7 +23695,7 @@
           <t>E | 462呎 (2房)
 $982万
 $21,260/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -23703,7 +23703,7 @@
           <t>F | 325呎 (1房)
 $596万
 $18,348/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -23711,7 +23711,7 @@
           <t>G | 265呎 (开放式)
 $487万
 $18,389/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -23719,7 +23719,7 @@
           <t>H | 324呎 (1房)
 $607万
 $18,722/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -23727,7 +23727,7 @@
           <t>J | 440呎 (2房)
 $837万
 $19,023/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -23735,7 +23735,7 @@
           <t>K | 437呎 (2房)
 $830万
 $18,993/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -23743,7 +23743,7 @@
           <t>L | 320呎 (1房)
 $579万
 $18,081/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
           <t>B | 628呎 (3房)
 $1387万
 $22,092/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -23774,7 +23774,7 @@
           <t>C | 420呎 (2房)
 $840万
 $20,000/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -23790,7 +23790,7 @@
           <t>E | 462呎 (2房)
 $989万
 $21,407/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -23798,7 +23798,7 @@
           <t>F | 325呎 (1房)
 $595万
 $18,302/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -23806,7 +23806,7 @@
           <t>G | 265呎 (开放式)
 $486万
 $18,340/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -23814,7 +23814,7 @@
           <t>H | 324呎 (1房)
 $592万
 $18,259/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -23822,7 +23822,7 @@
           <t>J | 440呎 (2房)
 $810万
 $18,409/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -23830,7 +23830,7 @@
           <t>K | 437呎 (2房)
 $803万
 $18,375/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -23838,7 +23838,7 @@
           <t>L | 320呎 (1房)
 $577万
 $18,034/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -23861,7 +23861,7 @@
           <t>B | 628呎 (3房)
 $1384万
 $22,037/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -23869,7 +23869,7 @@
           <t>C | 420呎 (2房)
 $820万
 $19,524/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -23877,7 +23877,7 @@
           <t>D | 477呎 (2房)
 $1023万
 $21,453/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -23885,7 +23885,7 @@
           <t>E | 462呎 (2房)
 $977万
 $21,152/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -23893,7 +23893,7 @@
           <t>F | 325呎 (1房)
 $593万
 $18,258/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -23901,7 +23901,7 @@
           <t>G | 265呎 (开放式)
 $510万
 $19,249/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -23909,7 +23909,7 @@
           <t>H | 324呎 (1房)
 $590万
 $18,213/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -23917,7 +23917,7 @@
           <t>J | 440呎 (2房)
 $808万
 $18,364/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -23925,7 +23925,7 @@
           <t>K | 437呎 (2房)
 $801万
 $18,330/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -23933,7 +23933,7 @@
           <t>L | 320呎 (1房)
 $602万
 $18,806/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -23956,7 +23956,7 @@
           <t>B | 628呎 (3房)
 $1365万
 $21,740/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -23964,7 +23964,7 @@
           <t>C | 420呎 (2房)
 $837万
 $19,929/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -23980,7 +23980,7 @@
           <t>E | 462呎 (2房)
 $946万
 $20,483/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -23988,7 +23988,7 @@
           <t>F | 325呎 (1房)
 $592万
 $18,212/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -23996,7 +23996,7 @@
           <t>G | 265呎 (开放式)
 $509万
 $19,200/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -24004,7 +24004,7 @@
           <t>H | 324呎 (1房)
 $589万
 $18,170/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -24012,7 +24012,7 @@
           <t>J | 440呎 (2房)
 $806万
 $18,318/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -24020,7 +24020,7 @@
           <t>K | 437呎 (2房)
 $799万
 $18,284/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -24028,7 +24028,7 @@
           <t>L | 320呎 (1房)
 $574万
 $17,944/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -24051,7 +24051,7 @@
           <t>B | 628呎 (3房)
 $1377万
 $21,925/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -24059,7 +24059,7 @@
           <t>C | 420呎 (2房)
 $824万
 $19,619/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -24067,7 +24067,7 @@
           <t>D | 477呎 (2房)
 $1008万
 $21,143/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -24075,7 +24075,7 @@
           <t>E | 462呎 (2房)
 $972万
 $21,048/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -24083,7 +24083,7 @@
           <t>F | 325呎 (1房)
 $590万
 $18,166/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -24091,7 +24091,7 @@
           <t>G | 265呎 (开放式)
 $508万
 $19,155/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -24099,7 +24099,7 @@
           <t>H | 324呎 (1房)
 $587万
 $18,123/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -24107,7 +24107,7 @@
           <t>J | 440呎 (2房)
 $804万
 $18,273/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -24115,7 +24115,7 @@
           <t>K | 437呎 (2房)
 $797万
 $18,238/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -24123,7 +24123,7 @@
           <t>L | 320呎 (1房)
 $573万
 $17,900/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -24146,7 +24146,7 @@
           <t>B | 628呎 (3房)
 $1374万
 $21,873/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -24154,7 +24154,7 @@
           <t>C | 420呎 (2房)
 $822万
 $19,571/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -24162,7 +24162,7 @@
           <t>D | 477呎 (2房)
 $1006万
 $21,092/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -24170,7 +24170,7 @@
           <t>E | 462呎 (2房)
 $942万
 $20,381/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -24178,7 +24178,7 @@
           <t>F | 325呎 (1房)
 $589万
 $18,120/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -24186,7 +24186,7 @@
           <t>G | 265呎 (开放式)
 $478万
 $18,057/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -24194,7 +24194,7 @@
           <t>H | 324呎 (1房)
 $586万
 $18,077/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -24202,7 +24202,7 @@
           <t>J | 440呎 (2房)
 $803万
 $18,250/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -24210,7 +24210,7 @@
           <t>K | 437呎 (2房)
 $795万
 $18,192/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -24218,7 +24218,7 @@
           <t>L | 320呎 (1房)
 $571万
 $17,853/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -24241,7 +24241,7 @@
           <t>B | 627呎 (3房)
 $1318万
 $21,016/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -24249,7 +24249,7 @@
           <t>C | 420呎 (2房)
 $819万
 $19,500/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -24257,7 +24257,7 @@
           <t>D | 477呎 (2房)
 $974万
 $20,423/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -24265,7 +24265,7 @@
           <t>E | 462呎 (2房)
 $939万
 $20,331/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -24273,7 +24273,7 @@
           <t>F | 325呎 (1房)
 $588万
 $18,077/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -24281,7 +24281,7 @@
           <t>G | 265呎 (开放式)
 $477万
 $18,015/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -24289,7 +24289,7 @@
           <t>H | 324呎 (1房)
 $584万
 $18,034/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -24297,7 +24297,7 @@
           <t>J | 440呎 (2房)
 $798万
 $18,136/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -24305,7 +24305,7 @@
           <t>K | 437呎 (2房)
 $793万
 $18,146/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -24313,7 +24313,7 @@
           <t>L | 320呎 (1房)
 $570万
 $17,809/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -24336,7 +24336,7 @@
           <t>B | 628呎 (3房)
 $1429万
 $22,752/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -24344,7 +24344,7 @@
           <t>C | 420呎 (2房)
 $809万
 $19,271/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -24360,7 +24360,7 @@
           <t>E | 462呎 (2房)
 $937万
 $20,279/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -24368,7 +24368,7 @@
           <t>F | 325呎 (1房)
 $586万
 $18,031/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -24376,7 +24376,7 @@
           <t>G | 265呎 (开放式)
 $504万
 $19,011/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -24384,7 +24384,7 @@
           <t>H | 324呎 (1房)
 $596万
 $18,395/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -24392,7 +24392,7 @@
           <t>J | 440呎 (2房)
 $798万
 $18,136/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -24400,7 +24400,7 @@
           <t>K | 437呎 (2房)
 $804万
 $18,400/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -24408,7 +24408,7 @@
           <t>L | 320呎 (1房)
 $568万
 $17,766/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -24423,7 +24423,7 @@
           <t>A | 439呎 (2房)
 $894万
 $20,376/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -24431,7 +24431,7 @@
           <t>B | 628呎 (3房)
 $1310万
 $20,860/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -24439,7 +24439,7 @@
           <t>C | 420呎 (2房)
 $808万
 $19,238/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -24447,7 +24447,7 @@
           <t>D | 477呎 (2房)
 $967万
 $20,270/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -24455,7 +24455,7 @@
           <t>E | 462呎 (2房)
 $923万
 $19,987/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -24463,7 +24463,7 @@
           <t>F | 325呎 (1房)
 $583万
 $17,942/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -24471,7 +24471,7 @@
           <t>G | 265呎 (开放式)
 $468万
 $17,679/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -24479,7 +24479,7 @@
           <t>H | 324呎 (1房)
 $580万
 $17,898/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -24487,7 +24487,7 @@
           <t>J | 440呎 (2房)
 $794万
 $18,045/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -24495,7 +24495,7 @@
           <t>K | 437呎 (2房)
 $785万
 $17,963/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -24503,7 +24503,7 @@
           <t>L | 320呎 (1房)
 $566万
 $17,678/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -24518,7 +24518,7 @@
           <t>A | 439呎 (2房)
 $892万
 $20,326/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -24526,7 +24526,7 @@
           <t>B | 628呎 (3房)
 $1305万
 $20,774/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -24534,7 +24534,7 @@
           <t>C | 420呎 (2房)
 $803万
 $19,126/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -24542,7 +24542,7 @@
           <t>D | 477呎 (2房)
 $919万
 $19,266/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -24550,7 +24550,7 @@
           <t>E | 462呎 (2房)
 $921万
 $19,933/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -24558,7 +24558,7 @@
           <t>F | 325呎 (1房)
 $582万
 $17,895/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -24566,7 +24566,7 @@
           <t>G | 265呎 (开放式)
 $467万
 $17,634/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -24574,7 +24574,7 @@
           <t>H | 324呎 (1房)
 $578万
 $17,855/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -24582,7 +24582,7 @@
           <t>J | 440呎 (2房)
 $790万
 $17,955/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -24590,7 +24590,7 @@
           <t>K | 437呎 (2房)
 $782万
 $17,897/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -24598,7 +24598,7 @@
           <t>L | 320呎 (1房)
 $564万
 $17,634/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -24613,7 +24613,7 @@
           <t>A | 439呎 (2房)
 $895万
 $20,387/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -24621,7 +24621,7 @@
           <t>B | 628呎 (3房)
 $1301万
 $20,723/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -24629,7 +24629,7 @@
           <t>C | 420呎 (2房)
 $810万
 $19,298/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -24637,7 +24637,7 @@
           <t>D | 477呎 (2房)
 $963万
 $20,189/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -24645,7 +24645,7 @@
           <t>E | 462呎 (2房)
 $919万
 $19,883/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -24653,7 +24653,7 @@
           <t>F | 325呎 (1房)
 $580万
 $17,852/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -24661,7 +24661,7 @@
           <t>G | 265呎 (开放式)
 $471万
 $17,789/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -24669,7 +24669,7 @@
           <t>H | 324呎 (1房)
 $577万
 $17,809/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -24677,7 +24677,7 @@
           <t>J | 440呎 (2房)
 $787万
 $17,893/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -24685,7 +24685,7 @@
           <t>K | 437呎 (2房)
 $780万
 $17,854/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -24693,7 +24693,7 @@
           <t>L | 320呎 (1房)
 $563万
 $17,591/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
           <t>B | 627呎 (3房)
 $1298万
 $20,703/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -24724,7 +24724,7 @@
           <t>C | 420呎 (2房)
 $799万
 $19,033/呎
-(25年-03月-16日)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -24732,7 +24732,7 @@
           <t>D | 477呎 (2房)
 $960万
 $20,119/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -24740,7 +24740,7 @@
           <t>E | 462呎 (2房)
 $916万
 $19,833/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -24748,7 +24748,7 @@
           <t>F | 325呎 (1房)
 $579万
 $17,806/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -24756,7 +24756,7 @@
           <t>G | 265呎 (开放式)
 $465万
 $17,547/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -24764,7 +24764,7 @@
           <t>H | 324呎 (1房)
 $576万
 $17,765/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -24772,7 +24772,7 @@
           <t>J | 440呎 (2房)
 $785万
 $17,848/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -24780,7 +24780,7 @@
           <t>K | 437呎 (2房)
 $778万
 $17,808/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -24788,7 +24788,7 @@
           <t>L | 320呎 (1房)
 $562万
 $17,547/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
     </row>
@@ -24803,7 +24803,7 @@
           <t>A | 439呎 (2房)
 $928万
 $21,144/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -24811,7 +24811,7 @@
           <t>B | 628呎 (3房)
 $1295万
 $20,619/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -24819,7 +24819,7 @@
           <t>C | 420呎 (2房)
 $797万
 $18,983/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -24827,7 +24827,7 @@
           <t>D | 477呎 (2房)
 $948万
 $19,876/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -24835,7 +24835,7 @@
           <t>E | 462呎 (2房)
 $914万
 $19,784/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -24843,7 +24843,7 @@
           <t>F | 325呎 (1房)
 $577万
 $17,763/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -24851,7 +24851,7 @@
           <t>G | 265呎 (开放式)
 $464万
 $17,502/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -24859,7 +24859,7 @@
           <t>H | 324呎 (1房)
 $574万
 $17,722/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -24867,7 +24867,7 @@
           <t>J | 441呎 (2房)
 $783万
 $17,762/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -24875,7 +24875,7 @@
           <t>K | 437呎 (2房)
 $776万
 $17,762/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -24883,7 +24883,7 @@
           <t>L | 320呎 (1房)
 $560万
 $17,503/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
     </row>
@@ -24898,7 +24898,7 @@
           <t>A | 439呎 (2房)
 $908万
 $20,688/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -24906,7 +24906,7 @@
           <t>B | 628呎 (3房)
 $1292万
 $20,567/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -24914,7 +24914,7 @@
           <t>C | 420呎 (2房)
 $795万
 $18,938/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -24922,7 +24922,7 @@
           <t>D | 477呎 (2房)
 $956万
 $20,042/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24930,7 +24930,7 @@
           <t>E | 462呎 (2房)
 $912万
 $19,736/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -24938,7 +24938,7 @@
           <t>F | 325呎 (1房)
 $576万
 $17,720/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -24946,7 +24946,7 @@
           <t>G | 265呎 (开放式)
 $463万
 $17,460/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -24954,7 +24954,7 @@
           <t>H | 324呎 (1房)
 $573万
 $17,676/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -24962,7 +24962,7 @@
           <t>J | 440呎 (2房)
 $790万
 $17,961/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -24970,7 +24970,7 @@
           <t>K | 437呎 (2房)
 $774万
 $17,719/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -24978,7 +24978,7 @@
           <t>L | 320呎 (1房)
 $565万
 $17,656/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -24993,7 +24993,7 @@
           <t>A | 439呎 (2房)
 $906万
 $20,638/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -25001,7 +25001,7 @@
           <t>B | 628呎 (3房)
 $1288万
 $20,518/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -25009,7 +25009,7 @@
           <t>C | 420呎 (2房)
 $793万
 $18,890/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -25017,7 +25017,7 @@
           <t>D | 477呎 (2房)
 $943万
 $19,776/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -25025,7 +25025,7 @@
           <t>E | 462呎 (2房)
 $890万
 $19,264/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -25033,7 +25033,7 @@
           <t>F | 325呎 (1房)
 $574万
 $17,674/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -25041,7 +25041,7 @@
           <t>G | 265呎 (开放式)
 $462万
 $17,415/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -25049,7 +25049,7 @@
           <t>H | 324呎 (1房)
 $571万
 $17,633/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -25057,7 +25057,7 @@
           <t>J | 440呎 (2房)
 $780万
 $17,716/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -25065,7 +25065,7 @@
           <t>K | 437呎 (2房)
 $781万
 $17,876/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -25073,7 +25073,7 @@
           <t>L | 320呎 (1房)
 $557万
 $17,416/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -25088,7 +25088,7 @@
           <t>A | 439呎 (2房)
 $904万
 $20,585/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -25096,7 +25096,7 @@
           <t>B | 627呎 (3房)
 $1285万
 $20,498/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -25104,7 +25104,7 @@
           <t>C | 420呎 (2房)
 $791万
 $18,843/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -25112,7 +25112,7 @@
           <t>D | 477呎 (2房)
 $941万
 $19,725/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -25120,7 +25120,7 @@
           <t>E | 462呎 (2房)
 $917万
 $19,853/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -25128,7 +25128,7 @@
           <t>F | 325呎 (1房)
 $573万
 $17,631/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -25136,7 +25136,7 @@
           <t>G | 265呎 (开放式)
 $460万
 $17,374/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -25144,7 +25144,7 @@
           <t>H | 324呎 (1房)
 $570万
 $17,586/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -25152,7 +25152,7 @@
           <t>J | 441呎 (2房)
 $778万
 $17,630/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -25160,7 +25160,7 @@
           <t>K | 437呎 (2房)
 $770万
 $17,632/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -25168,7 +25168,7 @@
           <t>L | 320呎 (1房)
 $556万
 $17,372/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25183,7 @@
           <t>A | 439呎 (2房)
 $901万
 $20,533/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -25191,7 +25191,7 @@
           <t>B | 627呎 (3房)
 $1297万
 $20,679/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -25199,7 +25199,7 @@
           <t>C | 420呎 (2房)
 $789万
 $18,795/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -25207,7 +25207,7 @@
           <t>D | 477呎 (2房)
 $939万
 $19,679/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -25215,7 +25215,7 @@
           <t>E | 462呎 (2房)
 $905万
 $19,589/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -25223,7 +25223,7 @@
           <t>F | 325呎 (1房)
 $572万
 $17,588/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -25231,7 +25231,7 @@
           <t>G | 265呎 (开放式)
 $459万
 $17,328/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -25239,7 +25239,7 @@
           <t>H | 324呎 (1房)
 $568万
 $17,543/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -25247,7 +25247,7 @@
           <t>J | 440呎 (2房)
 $776万
 $17,627/呎
-(25年-03月-16日)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -25255,7 +25255,7 @@
           <t>K | 437呎 (2房)
 $769万
 $17,588/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -25263,7 +25263,7 @@
           <t>L | 320呎 (1房)
 $554万
 $17,328/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
           <t>A | 439呎 (2房)
 $865万
 $19,704/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -25286,7 +25286,7 @@
           <t>B | 628呎 (3房)
 $1276万
 $20,312/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -25294,7 +25294,7 @@
           <t>C | 420呎 (2房)
 $786万
 $18,702/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -25302,7 +25302,7 @@
           <t>D | 477呎 (2房)
 $898万
 $18,832/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -25310,7 +25310,7 @@
           <t>E | 462呎 (2房)
 $867万
 $18,766/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -25318,7 +25318,7 @@
           <t>F | 325呎 (1房)
 $569万
 $17,498/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -25326,7 +25326,7 @@
           <t>G | 265呎 (开放式)
 $457万
 $17,242/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -25334,7 +25334,7 @@
           <t>H | 324呎 (1房)
 $566万
 $17,457/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -25342,7 +25342,7 @@
           <t>J | 440呎 (2房)
 $772万
 $17,539/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -25350,7 +25350,7 @@
           <t>K | 437呎 (2房)
 $765万
 $17,499/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -25358,7 +25358,7 @@
           <t>L | 320呎 (1房)
 $552万
 $17,241/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
           <t>A | 439呎 (2房)
 $860万
 $19,601/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -25381,7 +25381,7 @@
           <t>B | 628呎 (3房)
 $1272万
 $20,261/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -25389,7 +25389,7 @@
           <t>C | 420呎 (2房)
 $792万
 $18,867/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -25397,7 +25397,7 @@
           <t>D | 477呎 (2房)
 $916万
 $19,210/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -25405,7 +25405,7 @@
           <t>E | 462呎 (2房)
 $864万
 $18,699/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -25413,7 +25413,7 @@
           <t>F | 325呎 (1房)
 $567万
 $17,455/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -25421,7 +25421,7 @@
           <t>G | 265呎 (开放式)
 $456万
 $17,200/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -25429,7 +25429,7 @@
           <t>H | 324呎 (1房)
 $564万
 $17,414/呎
-(25年-01月-08日)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -25437,7 +25437,7 @@
           <t>J | 440呎 (2房)
 $778万
 $17,693/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -25445,7 +25445,7 @@
           <t>K | 437呎 (2房)
 $763万
 $17,455/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -25453,7 +25453,7 @@
           <t>L | 320呎 (1房)
 $550万
 $17,200/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25468,7 @@
           <t>A | 439呎 (2房)
 $892万
 $20,330/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -25476,7 +25476,7 @@
           <t>B | 628呎 (3房)
 $1269万
 $20,212/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -25484,7 +25484,7 @@
           <t>C | 420呎 (2房)
 $782万
 $18,610/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -25492,7 +25492,7 @@
           <t>D | 477呎 (2房)
 $938万
 $19,673/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -25500,7 +25500,7 @@
           <t>E | 462呎 (2房)
 $870万
 $18,840/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -25508,7 +25508,7 @@
           <t>F | 325呎 (1房)
 $572万
 $17,609/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -25516,7 +25516,7 @@
           <t>G | 265呎 (开放式)
 $455万
 $17,158/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -25524,7 +25524,7 @@
           <t>H | 324呎 (1房)
 $563万
 $17,370/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -25532,7 +25532,7 @@
           <t>J | 441呎 (2房)
 $768万
 $17,410/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -25540,7 +25540,7 @@
           <t>K | 437呎 (2房)
 $761万
 $17,412/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -25548,7 +25548,7 @@
           <t>L | 320呎 (1房)
 $549万
 $17,156/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -25563,7 +25563,7 @@
           <t>A | 439呎 (2房)
 $866万
 $19,727/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -25571,7 +25571,7 @@
           <t>B | 628呎 (3房)
 $1266万
 $20,161/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -25579,7 +25579,7 @@
           <t>C | 420呎 (2房)
 $780万
 $18,562/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -25587,7 +25587,7 @@
           <t>D | 477呎 (2房)
 $936万
 $19,625/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -25595,7 +25595,7 @@
           <t>E | 462呎 (2房)
 $879万
 $19,028/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -25603,7 +25603,7 @@
           <t>F | 325呎 (1房)
 $564万
 $17,369/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -25611,7 +25611,7 @@
           <t>G | 265呎 (开放式)
 $454万
 $17,113/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -25619,7 +25619,7 @@
           <t>H | 324呎 (1房)
 $561万
 $17,327/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -25627,7 +25627,7 @@
           <t>J | 440呎 (2房)
 $766万
 $17,407/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -25635,7 +25635,7 @@
           <t>K | 437呎 (2房)
 $768万
 $17,568/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -25643,7 +25643,7 @@
           <t>L | 320呎 (1房)
 $548万
 $17,112/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25658,7 @@
           <t>A | 439呎 (2房)
 $863万
 $19,658/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -25666,7 +25666,7 @@
           <t>B | 627呎 (3房)
 $1263万
 $20,142/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -25674,7 +25674,7 @@
           <t>C | 420呎 (2房)
 $778万
 $18,517/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -25682,7 +25682,7 @@
           <t>D | 477呎 (2房)
 $890万
 $18,658/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -25690,7 +25690,7 @@
           <t>E | 462呎 (2房)
 $857万
 $18,558/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -25698,7 +25698,7 @@
           <t>F | 325呎 (1房)
 $563万
 $17,326/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -25706,7 +25706,7 @@
           <t>G | 265呎 (开放式)
 $452万
 $17,072/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -25714,7 +25714,7 @@
           <t>H | 324呎 (1房)
 $560万
 $17,284/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -25722,7 +25722,7 @@
           <t>J | 440呎 (2房)
 $764万
 $17,366/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -25730,7 +25730,7 @@
           <t>K | 437呎 (2房)
 $757万
 $17,325/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -25738,7 +25738,7 @@
           <t>L | 320呎 (1房)
 $546万
 $17,072/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25761,7 @@
           <t>B | 627呎 (3房)
 $1260万
 $20,094/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -25769,7 +25769,7 @@
           <t>C | 420呎 (2房)
 $776万
 $18,471/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -25777,7 +25777,7 @@
           <t>D | 477呎 (2房)
 $922万
 $19,338/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -25785,7 +25785,7 @@
           <t>E | 462呎 (2房)
 $855万
 $18,513/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -25793,7 +25793,7 @@
           <t>F | 325呎 (1房)
 $587万
 $18,068/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -25801,7 +25801,7 @@
           <t>G | 265呎 (开放式)
 $451万
 $17,026/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -25809,7 +25809,7 @@
           <t>H | 324呎 (1房)
 $559万
 $17,241/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -25817,7 +25817,7 @@
           <t>J | 440呎 (2房)
 $762万
 $17,320/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -25825,7 +25825,7 @@
           <t>K | 437呎 (2房)
 $755万
 $17,284/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
@@ -25833,7 +25833,7 @@
           <t>L | 320呎 (1房)
 $570万
 $17,800/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -25848,7 +25848,7 @@
           <t>A | 439呎 (2房)
 $899万
 $20,478/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -25856,7 +25856,7 @@
           <t>B | 627呎 (3房)
 $1242万
 $19,802/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -25864,7 +25864,7 @@
           <t>C | 420呎 (2房)
 $774万
 $18,424/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -25872,7 +25872,7 @@
           <t>D | 477呎 (2房)
 $930万
 $19,497/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -25880,7 +25880,7 @@
           <t>E | 462呎 (2房)
 $863万
 $18,675/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -25888,7 +25888,7 @@
           <t>F | 325呎 (1房)
 $586万
 $18,022/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -25896,7 +25896,7 @@
           <t>G | 265呎 (开放式)
 $450万
 $16,989/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -25904,7 +25904,7 @@
           <t>H | 324呎 (1房)
 $557万
 $17,198/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -25912,7 +25912,7 @@
           <t>J | 440呎 (2房)
 $760万
 $17,280/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -25920,7 +25920,7 @@
           <t>K | 437呎 (2房)
 $753万
 $17,238/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -25928,7 +25928,7 @@
           <t>L | 320呎 (1房)
 $544万
 $16,984/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -25943,7 +25943,7 @@
           <t>A | 439呎 (2房)
 $885万
 $20,169/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -25951,7 +25951,7 @@
           <t>B | 628呎 (3房)
 $1258万
 $20,040/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -25959,7 +25959,7 @@
           <t>C | 420呎 (2房)
 $781万
 $18,588/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -25967,7 +25967,7 @@
           <t>D | 477呎 (2房)
 $928万
 $19,455/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -25975,7 +25975,7 @@
           <t>E | 462呎 (2房)
 $866万
 $18,734/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -25983,7 +25983,7 @@
           <t>F | 325呎 (1房)
 $584万
 $17,978/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -25991,7 +25991,7 @@
           <t>G | 265呎 (开放式)
 $449万
 $16,943/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -25999,7 +25999,7 @@
           <t>H | 324呎 (1房)
 $556万
 $17,154/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -26007,7 +26007,7 @@
           <t>J | 440呎 (2房)
 $767万
 $17,432/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -26015,7 +26015,7 @@
           <t>K | 437呎 (2房)
 $760万
 $17,391/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">
@@ -26023,7 +26023,7 @@
           <t>L | 320呎 (1房)
 $548万
 $17,138/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
           <t>D | 480呎 (2房)
 $927万
 $19,308/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -26049,7 +26049,7 @@
           <t>E | 462呎 (2房)
 $847万
 $18,329/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -26057,7 +26057,7 @@
           <t>F | 325呎 (1房)
 $578万
 $17,800/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -26065,7 +26065,7 @@
           <t>G | 265呎 (开放式)
 $444万
 $16,774/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -26073,7 +26073,7 @@
           <t>H | 324呎 (1房)
 $550万
 $16,985/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -26081,7 +26081,7 @@
           <t>J | 446呎 (2房)
 $758万
 $16,987/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr"/>
@@ -26101,7 +26101,7 @@
           <t>D | 480呎 (2房)
 $917万
 $19,098/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -26109,7 +26109,7 @@
           <t>E | 462呎 (2房)
 $859万
 $18,595/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -26117,7 +26117,7 @@
           <t>F | 325呎 (1房)
 $577万
 $17,757/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -26125,7 +26125,7 @@
           <t>G | 265呎 (开放式)
 $443万
 $16,732/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>H | 324呎 (1房)
 $549万
 $16,941/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>J | 446呎 (2房)
 $756万
 $16,944/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr"/>
@@ -26161,7 +26161,7 @@
           <t>D | 480呎 (2房)
 $923万
 $19,235/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -26169,7 +26169,7 @@
           <t>E | 462呎 (2房)
 $876万
 $18,963/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -26177,7 +26177,7 @@
           <t>F | 325呎 (1房)
 $576万
 $17,711/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -26185,7 +26185,7 @@
           <t>G | 265呎 (开放式)
 $442万
 $16,691/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -26193,7 +26193,7 @@
           <t>H | 324呎 (1房)
 $548万
 $16,898/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -26201,7 +26201,7 @@
           <t>J | 446呎 (2房)
 $780万
 $17,480/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="K35" s="21" t="inlineStr"/>
@@ -26221,7 +26221,7 @@
           <t>D | 480呎 (2房)
 $921万
 $19,188/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -26229,7 +26229,7 @@
           <t>E | 336呎 (1房)
 $610万
 $18,161/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -26237,7 +26237,7 @@
           <t>F | 325呎 (1房)
 $568万
 $17,489/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -26245,7 +26245,7 @@
           <t>G | 265呎 (开放式)
 $437万
 $16,483/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -26253,7 +26253,7 @@
           <t>H | 324呎 (1房)
 $541万
 $16,688/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
@@ -26261,7 +26261,7 @@
           <t>J | 446呎 (2房)
 $770万
 $17,260/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="K36" s="21" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
           <t>D | 480呎 (2房)
 $919万
 $19,140/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -26289,7 +26289,7 @@
           <t>E | 336呎 (1房)
 $609万
 $18,116/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -26297,7 +26297,7 @@
           <t>F | 326呎 (1房)
 $535万
 $16,405/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -26305,7 +26305,7 @@
           <t>G | 265呎 (开放式)
 $427万
 $16,113/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -26313,7 +26313,7 @@
           <t>H | 324呎 (1房)
 $541万
 $16,685/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -26321,7 +26321,7 @@
           <t>J | 446呎 (2房)
 $728万
 $16,316/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr"/>
@@ -26341,7 +26341,7 @@
           <t>D | 480呎 (2房)
 $944万
 $19,667/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -26349,7 +26349,7 @@
           <t>E | 297呎 (1房)
 $632万
 $21,293/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -26357,7 +26357,7 @@
           <t>F | 327呎 (1房)
 $538万
 $16,459/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>G | 265呎 (开放式)
 $422万
 $15,943/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>H | 324呎 (1房)
 $541万
 $16,694/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>J | 446呎 (2房)
 $720万
 $16,148/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr"/>
@@ -26527,7 +26527,7 @@
           <t>A | 426呎 (2房)
 $953万
 $22,371/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -26535,7 +26535,7 @@
           <t>B | 437呎 (2房)
 $1000万
 $22,883/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -26543,7 +26543,7 @@
           <t>C | 609呎 (3房)
 $1628万
 $26,732/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -26560,7 +26560,7 @@
           <t>A | 427呎 (2房)
 $816万
 $19,117/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>B | 436呎 (2房)
 $871万
 $19,977/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>C | 305呎 (1房)
 $620万
 $20,315/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>D | 304呎 (1房)
 $620万
 $20,382/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>E | 439呎 (2房)
 $902万
 $20,549/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
           <t>A | 427呎 (2房)
 $811万
 $19,002/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -26615,7 +26615,7 @@
           <t>B | 436呎 (2房)
 $866万
 $19,858/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -26623,7 +26623,7 @@
           <t>C | 305呎 (1房)
 $616万
 $20,193/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -26631,7 +26631,7 @@
           <t>D | 304呎 (1房)
 $616万
 $20,260/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -26639,7 +26639,7 @@
           <t>E | 439呎 (2房)
 $897万
 $20,428/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -26654,7 +26654,7 @@
           <t>A | 427呎 (2房)
 $807万
 $18,890/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -26662,7 +26662,7 @@
           <t>B | 436呎 (2房)
 $861万
 $19,741/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -26670,7 +26670,7 @@
           <t>C | 305呎 (1房)
 $612万
 $20,072/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -26678,7 +26678,7 @@
           <t>D | 305呎 (1房)
 $612万
 $20,072/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -26686,7 +26686,7 @@
           <t>E | 439呎 (2房)
 $892万
 $20,308/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -26701,7 +26701,7 @@
           <t>A | 390呎 (2房)
 $850万
 $21,795/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -26709,7 +26709,7 @@
           <t>B | 398呎 (2房)
 $1020万
 $25,628/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -26717,7 +26717,7 @@
           <t>C | 267呎 (1房)
 $640万
 $23,970/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -26725,7 +26725,7 @@
           <t>D | 267呎 (1房)
 $662万
 $24,794/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -26733,7 +26733,7 @@
           <t>E | 445呎 (2房)
 $1135万
 $25,506/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Double Coast I.xlsx
+++ b/files/九龙-启德-Double Coast I.xlsx
@@ -21787,7 +21787,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -26341,7 +26341,7 @@
           <t>D | 480呎 (2房)
 $944万
 $19,667/呎
-(26年-07月-08日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">

--- a/files/九龙-启德-Double Coast I.xlsx
+++ b/files/九龙-启德-Double Coast I.xlsx
@@ -10668,38 +10668,30 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>9760000</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>22182</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K161" s="5" t="n">
+        <v>9760000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>22182</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -10708,7 +10700,7 @@
       </c>
       <c r="N161" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23323,7 +23315,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23333,7 +23325,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24703,12 +24695,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
-招标单位
--
-(在售)</t>
+$976万
+$22,182/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
